--- a/data/trans_dic/P1438_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1438_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,12</t>
+          <t>2,18; 5,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,42</t>
+          <t>4,06; 7,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,75</t>
+          <t>3,33; 5,62</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,55</t>
+          <t>1,29; 3,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,3</t>
+          <t>3,72; 7,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,81</t>
+          <t>2,71; 4,72</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,39</t>
+          <t>4,52; 8,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 14,58</t>
+          <t>7,55; 14,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,33</t>
+          <t>6,06; 9,77</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,57</t>
+          <t>4,61; 7,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,7</t>
+          <t>5,88; 8,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,06</t>
+          <t>5,57; 7,38</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,9</t>
+          <t>4,08; 7,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 13,7</t>
+          <t>11,11; 14,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,24</t>
+          <t>8,6; 11,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,68</t>
+          <t>7,36; 10,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,36</t>
+          <t>5,8; 8,45</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,26</t>
+          <t>4,03; 5,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 8,84</t>
+          <t>7,91; 9,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,85</t>
+          <t>6,19; 7,16</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>19211</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24253</t>
+          <t>27046</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41038</t>
+          <t>46258</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10171; 25821</t>
+          <t>12000; 30642</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17748; 33194</t>
+          <t>19836; 37000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31685; 54718</t>
+          <t>34590; 58320</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30931</t>
+          <t>32895</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6088; 16037</t>
+          <t>6257; 16168</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14506; 27880</t>
+          <t>15673; 30008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23989; 40118</t>
+          <t>24542; 42723</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>50287</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9378; 49305</t>
+          <t>21295; 42321</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12541; 24334</t>
+          <t>14161; 27755</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20902; 69539</t>
+          <t>39917; 64301</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>66311</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>62727</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118313</t>
+          <t>129038</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50247; 78251</t>
+          <t>52132; 82697</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29873; 75309</t>
+          <t>50607; 75895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84698; 141970</t>
+          <t>110881; 147098</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>97242</t>
+          <t>105387</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128089</t>
+          <t>137534</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21787; 42204</t>
+          <t>23130; 43472</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72257; 114951</t>
+          <t>92250; 121275</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101651; 147632</t>
+          <t>120104; 156057</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>67749</t>
+          <t>74038</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68975</t>
+          <t>75256</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5495</t>
+          <t>0; 4238</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56965; 81243</t>
+          <t>62088; 89068</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56562; 83666</t>
+          <t>62655; 91362</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>150273</t>
+          <t>159879</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>283445</t>
+          <t>311388</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>433719</t>
+          <t>471268</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>118423; 177477</t>
+          <t>138592; 183516</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>235558; 315957</t>
+          <t>287432; 338248</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>376983; 475968</t>
+          <t>437392; 506438</t>
         </is>
       </c>
     </row>
